--- a/outputs/ASA1_report.xlsx
+++ b/outputs/ASA1_report.xlsx
@@ -534,7 +534,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Audit Run: 2026-10-14 16:59:17 | Total Devices: 1</t>
+          <t>Audit Run: 2026-10-15 10:52:26 | Total Devices: 1</t>
         </is>
       </c>
     </row>
